--- a/artfynd/A 54368-2024 artfynd.xlsx
+++ b/artfynd/A 54368-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123729912</v>
       </c>
       <c r="B2" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>123733326</v>
       </c>
       <c r="B3" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 54368-2024 artfynd.xlsx
+++ b/artfynd/A 54368-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123729912</v>
       </c>
       <c r="B2" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>123733326</v>
       </c>
       <c r="B3" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 54368-2024 artfynd.xlsx
+++ b/artfynd/A 54368-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123729912</v>
+        <v>123733326</v>
       </c>
       <c r="B2" t="n">
         <v>57644</v>
@@ -710,15 +710,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -731,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616616</v>
+        <v>616561</v>
       </c>
       <c r="R2" t="n">
-        <v>6647269</v>
+        <v>6647232</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -766,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -776,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -808,7 +804,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123733326</v>
+        <v>123729912</v>
       </c>
       <c r="B3" t="n">
         <v>57644</v>
@@ -843,11 +839,15 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616561</v>
+        <v>616616</v>
       </c>
       <c r="R3" t="n">
-        <v>6647232</v>
+        <v>6647269</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54368-2024 artfynd.xlsx
+++ b/artfynd/A 54368-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123733326</v>
+        <v>123729912</v>
       </c>
       <c r="B2" t="n">
         <v>57644</v>
@@ -710,11 +710,15 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -727,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616561</v>
+        <v>616616</v>
       </c>
       <c r="R2" t="n">
-        <v>6647232</v>
+        <v>6647269</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -762,7 +766,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +776,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,7 +808,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123729912</v>
+        <v>123733326</v>
       </c>
       <c r="B3" t="n">
         <v>57644</v>
@@ -839,15 +843,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616616</v>
+        <v>616561</v>
       </c>
       <c r="R3" t="n">
-        <v>6647269</v>
+        <v>6647232</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54368-2024 artfynd.xlsx
+++ b/artfynd/A 54368-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123733326</v>
+        <v>123729912</v>
       </c>
       <c r="B2" t="n">
         <v>57666</v>
@@ -710,11 +710,15 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -727,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616561</v>
+        <v>616616</v>
       </c>
       <c r="R2" t="n">
-        <v>6647232</v>
+        <v>6647269</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -762,7 +766,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +776,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,7 +808,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123729912</v>
+        <v>123733326</v>
       </c>
       <c r="B3" t="n">
         <v>57666</v>
@@ -839,15 +843,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616616</v>
+        <v>616561</v>
       </c>
       <c r="R3" t="n">
-        <v>6647269</v>
+        <v>6647232</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54368-2024 artfynd.xlsx
+++ b/artfynd/A 54368-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>123729912</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,12 +806,7 @@
         <v>123733326</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54368-2024 artfynd.xlsx
+++ b/artfynd/A 54368-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123729912</v>
       </c>
       <c r="B2" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>123733326</v>
       </c>
       <c r="B3" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54368-2024 artfynd.xlsx
+++ b/artfynd/A 54368-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123729912</v>
       </c>
       <c r="B2" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>123733326</v>
       </c>
       <c r="B3" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54368-2024 artfynd.xlsx
+++ b/artfynd/A 54368-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123729912</v>
       </c>
       <c r="B2" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>123733326</v>
       </c>
       <c r="B3" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54368-2024 artfynd.xlsx
+++ b/artfynd/A 54368-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123729912</v>
       </c>
       <c r="B2" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>123733326</v>
       </c>
       <c r="B3" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54368-2024 artfynd.xlsx
+++ b/artfynd/A 54368-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123729912</v>
       </c>
       <c r="B2" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>123733326</v>
       </c>
       <c r="B3" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54368-2024 artfynd.xlsx
+++ b/artfynd/A 54368-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123729912</v>
       </c>
       <c r="B2" t="n">
-        <v>58063</v>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>123733326</v>
       </c>
       <c r="B3" t="n">
-        <v>58063</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54368-2024 artfynd.xlsx
+++ b/artfynd/A 54368-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -800,6 +805,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123729912</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,8 +934,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123733326</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>